--- a/output/2026-09-14_21_Croazia_Virovitico-podravska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-14_21_Croazia_Virovitico-podravska_Depolverazione_Trattamento_aria.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Catena nazionale bricolage/ferramenta/edilizia (sede legale Sesvete); punto vendita di Virovitica (Ote Horvata 4) vende aspiratori industriali dust/wet-dry e attrezzatura da cantiere. Indirizzo, telefono ed email confermati su fonti multiple (pevex.hr, mojkatalog.hr, polomap.com). Rivenditore generalista, non specializzato in filtrazione industriale.</t>
+          <t>Catena nazionale bricolage/ferramenta/edilizia (sede legale Sesvete); punto vendita di Virovitica (Ote Horvata 4) vende aspiratori industriali dust/wet-dry e attrezzatura da cantiere. Indirizzo, telefono ed email confermati su fonti multiple (pevex.hr, mojkatalog.hr, polomap.com). Rivenditore generalista, non specializzato in filtrazione industriale. [DUPLICATO — vedi anche: 2026-09-14_03_Croazia_Licko-senjska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
